--- a/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>MONTESSORI DE VILLA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.2184</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.93516</v>
-      </c>
-      <c r="I2" t="n">
-        <v>214</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.2184</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.93516</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>517 MIS PEQUEÑITOS ANGELITOS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.21541</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.93716999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>239</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.21541</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.93717</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>526 SANTISIMA VIRGEN DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.21002</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.9401</v>
-      </c>
-      <c r="I4" t="n">
-        <v>253</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.21002</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.9401</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>557</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.2286</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.92331</v>
-      </c>
-      <c r="I5" t="n">
-        <v>392</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.2286</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.92331</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>558 CASA MONTESSORI</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.2322</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.92093</v>
-      </c>
-      <c r="I6" t="n">
-        <v>300</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.2322</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.92093</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>628</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.21923</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.92286</v>
-      </c>
-      <c r="I7" t="n">
-        <v>330</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.21923</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.92286</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>652</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.22285</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.9393</v>
-      </c>
-      <c r="I8" t="n">
-        <v>363</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.22285</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.9393</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>652 02 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.23838</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.92429</v>
-      </c>
-      <c r="I9" t="n">
-        <v>227</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.23838</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.92429</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>652 03 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.23834</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.91759</v>
-      </c>
-      <c r="I10" t="n">
-        <v>235</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.23834</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.91759</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>652 11 PEQUEÑOS QUERUBINES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.21539</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.94935</v>
-      </c>
-      <c r="I11" t="n">
-        <v>227</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.21539</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.94935</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>652 10</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.1913</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.94121</v>
-      </c>
-      <c r="I12" t="n">
-        <v>272</v>
-      </c>
-      <c r="J12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.1913</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.94121</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>652-17 CAPULLITO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.22614</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.9205</v>
-      </c>
-      <c r="I13" t="n">
-        <v>390</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.22614</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.9205</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>652 22 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.20616</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.95102</v>
-      </c>
-      <c r="I14" t="n">
-        <v>506</v>
-      </c>
-      <c r="J14" t="n">
-        <v>22</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.20616</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.95102</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>652 24 / 7232 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.21488</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.95469</v>
-      </c>
-      <c r="I15" t="n">
-        <v>522</v>
-      </c>
-      <c r="J15" t="n">
-        <v>29</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.21488</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.95469</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>6004 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.19548</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.96105</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1166</v>
-      </c>
-      <c r="J16" t="n">
-        <v>61</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.19548</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.96105</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>6063 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.20085</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.94336</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1515</v>
-      </c>
-      <c r="J17" t="n">
-        <v>75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.20085</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.94336</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>6064 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.21011</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.93622000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1473</v>
-      </c>
-      <c r="J18" t="n">
-        <v>75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.21011</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.93622</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>6065 PERU INGLATERRA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.2076</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.9419</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1604</v>
-      </c>
-      <c r="J19" t="n">
-        <v>72</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.2076</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.9419</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>6066 VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.21334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.93987</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2593</v>
-      </c>
-      <c r="J20" t="n">
-        <v>130</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.21334</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.93987</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>6067 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.2244361218332</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.9282762820025</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1021</v>
-      </c>
-      <c r="J21" t="n">
-        <v>56</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.2244361218332</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.9282762820025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>6068 MANUEL GONZALES PRADA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.22581</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.93209</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="J22" t="n">
-        <v>81</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.22581</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.93209</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>6069 PACHACUTEC</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.21846</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.93606</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1852</v>
-      </c>
-      <c r="J23" t="n">
-        <v>78</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.21846</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.93606</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1852</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.2239</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.94643000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2337</v>
-      </c>
-      <c r="J24" t="n">
-        <v>97</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.2239</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.94643</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>6076 REPUBLICA DE NICARAGUA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.2201</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.93966</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1370</v>
-      </c>
-      <c r="J25" t="n">
-        <v>55</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.2201</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.93966</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.21089</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.95359999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1357</v>
-      </c>
-      <c r="J26" t="n">
-        <v>61</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.21089</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.9536</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>7077 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.21796</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.96735</v>
-      </c>
-      <c r="I27" t="n">
-        <v>386</v>
-      </c>
-      <c r="J27" t="n">
-        <v>21</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.21796</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.96735</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>7084 PERUANO SUIZO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.22934</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.92323</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1704</v>
-      </c>
-      <c r="J28" t="n">
-        <v>81</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.22934</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.92323</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>7090 FORJADORES DEL PERU</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.19227</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.94150999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>388</v>
-      </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.19227</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.94151</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>7091 REPUBLICA DEL PERU</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.22856</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.94364</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2327</v>
-      </c>
-      <c r="J30" t="n">
-        <v>79</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.22856</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.94364</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>7092 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.18848</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.94866</v>
-      </c>
-      <c r="I31" t="n">
-        <v>487</v>
-      </c>
-      <c r="J31" t="n">
-        <v>25</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.18848</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.94866</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>7093 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.2293</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.93405</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1371</v>
-      </c>
-      <c r="J32" t="n">
-        <v>66</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.2293</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.93405</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>7094 SASAKAWA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.20551</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.95434</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J33" t="n">
-        <v>67</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.20551</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.95434</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>7095 PERU ITALIA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.19393</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.95851</v>
-      </c>
-      <c r="I34" t="n">
-        <v>625</v>
-      </c>
-      <c r="J34" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.19393</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.95851</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>7097 VILLA AMSTELVEEN</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.21664</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.93277999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>782</v>
-      </c>
-      <c r="J35" t="n">
-        <v>33</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.21664</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.93278</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.2369</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.92089</v>
-      </c>
-      <c r="I36" t="n">
-        <v>646</v>
-      </c>
-      <c r="J36" t="n">
-        <v>27</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.2369</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.92089</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>7216</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.19661</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.96223000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>603</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.19661</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.96223</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>REPUBLICA DE BOLIVIA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.19653</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.94983000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1990</v>
-      </c>
-      <c r="J38" t="n">
-        <v>96</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.19653</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.94983</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.23982</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.91742000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>938</v>
-      </c>
-      <c r="J39" t="n">
-        <v>53</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.23982</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.91742</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>7228 PERUANO CANADIENSE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.23977</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.92488</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1775</v>
-      </c>
-      <c r="J40" t="n">
-        <v>86</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.23977</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.92488</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>7234 / 7234 LAS PALMERAS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.248</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.93124</v>
-      </c>
-      <c r="I41" t="n">
-        <v>593</v>
-      </c>
-      <c r="J41" t="n">
-        <v>30</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.248</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.93124</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>7237 PERU VALLADOLID</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.24054</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.93255000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1217</v>
-      </c>
-      <c r="J42" t="n">
-        <v>56</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.24054</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.93255</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>7236 MAX UHLE</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.24546</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.91862</v>
-      </c>
-      <c r="I43" t="n">
-        <v>846</v>
-      </c>
-      <c r="J43" t="n">
-        <v>54</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.24546</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.91862</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.21623</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.93049999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>480</v>
-      </c>
-      <c r="J44" t="n">
-        <v>18</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.21623</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.9305</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.23802</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.93899</v>
-      </c>
-      <c r="I45" t="n">
-        <v>915</v>
-      </c>
-      <c r="J45" t="n">
-        <v>43</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.23802</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.93899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>7240 JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.24413</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.92919000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1139</v>
-      </c>
-      <c r="J46" t="n">
-        <v>47</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.24413</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.92919</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>7241</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.24311</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.94398</v>
-      </c>
-      <c r="I47" t="n">
-        <v>208</v>
-      </c>
-      <c r="J47" t="n">
-        <v>9</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.24311</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.94398</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>ADVENTISTA SALVADOR</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.19922</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.95228</v>
-      </c>
-      <c r="I48" t="n">
-        <v>467</v>
-      </c>
-      <c r="J48" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.19922</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.95228</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>BARTOLOME HERRERA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.19965</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.95050999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>205</v>
-      </c>
-      <c r="J49" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.19965</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.95051</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>BENJAMIN FRANKLIN</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.22252</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.92628999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>198</v>
-      </c>
-      <c r="J50" t="n">
-        <v>18</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.22252</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.92629</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>CRISTO REY DE VILLA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.20437</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.93648</v>
-      </c>
-      <c r="I51" t="n">
-        <v>334</v>
-      </c>
-      <c r="J51" t="n">
-        <v>30</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.20437</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.93648</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>EL DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.23037</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.92559</v>
-      </c>
-      <c r="I52" t="n">
-        <v>510</v>
-      </c>
-      <c r="J52" t="n">
-        <v>25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.23037</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.92559</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>EMMANUEL</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.22194</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.92251</v>
-      </c>
-      <c r="I53" t="n">
-        <v>392</v>
-      </c>
-      <c r="J53" t="n">
-        <v>18</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.22194</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.92251</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>HANS CHRISTIAN ANDERSEN</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.21006</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.9396</v>
-      </c>
-      <c r="I54" t="n">
-        <v>96</v>
-      </c>
-      <c r="J54" t="n">
-        <v>20</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.21006</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.9396</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>JOHN VON NEUMANN</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.21938</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.93037</v>
-      </c>
-      <c r="I55" t="n">
-        <v>128</v>
-      </c>
-      <c r="J55" t="n">
-        <v>10</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.21938</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.93037</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>JUAN XXIII</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.19282</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.95905</v>
-      </c>
-      <c r="I56" t="n">
-        <v>226</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.19282</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.95905</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.22566</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.94213000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>334</v>
-      </c>
-      <c r="J57" t="n">
-        <v>29</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.22566</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.94213</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.23934</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-76.92321</v>
-      </c>
-      <c r="I58" t="n">
-        <v>338</v>
-      </c>
-      <c r="J58" t="n">
-        <v>22</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.23934</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-76.92321</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.2019</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-76.95480999999999</v>
-      </c>
-      <c r="I59" t="n">
-        <v>753</v>
-      </c>
-      <c r="J59" t="n">
-        <v>44</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.2019</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-76.95481</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>PATRON SANTIAGO DE YANACA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.2225</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-76.95098</v>
-      </c>
-      <c r="I60" t="n">
-        <v>310</v>
-      </c>
-      <c r="J60" t="n">
-        <v>18</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.2225</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-76.95098</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SEBASTIAN LORENTE</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.23022</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.94175</v>
-      </c>
-      <c r="I61" t="n">
-        <v>203</v>
-      </c>
-      <c r="J61" t="n">
-        <v>19</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.23022</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.94175</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.22662</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-76.92649</v>
-      </c>
-      <c r="I62" t="n">
-        <v>305</v>
-      </c>
-      <c r="J62" t="n">
-        <v>8</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.22662</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-76.92649</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>MERCEDES CABELLO DE CARBONERA</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.22478</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-76.93294</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.22478</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-76.93294</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>PROLOG DE VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.22776</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-76.92756</v>
-      </c>
-      <c r="I64" t="n">
-        <v>946</v>
-      </c>
-      <c r="J64" t="n">
-        <v>51</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.22776</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-76.92756</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>HIPOLITO UNANUE</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.21541</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-76.94492</v>
-      </c>
-      <c r="I65" t="n">
-        <v>379</v>
-      </c>
-      <c r="J65" t="n">
-        <v>34</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.21541</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-76.94492</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.19373</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-76.96147999999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>150</v>
-      </c>
-      <c r="J66" t="n">
-        <v>15</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.19373</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-76.96148</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.20411</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-76.94568</v>
-      </c>
-      <c r="I67" t="n">
-        <v>365</v>
-      </c>
-      <c r="J67" t="n">
-        <v>20</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.20411</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-76.94568</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>MI DULCE JESUS</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.22169</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-76.94446000000001</v>
-      </c>
-      <c r="I68" t="n">
-        <v>238</v>
-      </c>
-      <c r="J68" t="n">
-        <v>14</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.22169</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-76.94446</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO DE VILLA</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.24192</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-76.92701</v>
-      </c>
-      <c r="I69" t="n">
-        <v>255</v>
-      </c>
-      <c r="J69" t="n">
-        <v>17</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.24192</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-76.92701</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.22297</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-76.94141999999999</v>
-      </c>
-      <c r="I70" t="n">
-        <v>210</v>
-      </c>
-      <c r="J70" t="n">
-        <v>14</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.22297</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-76.94142</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.19354</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-76.95428</v>
-      </c>
-      <c r="I71" t="n">
-        <v>218</v>
-      </c>
-      <c r="J71" t="n">
-        <v>17</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.19354</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-76.95428</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.21069</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-76.9388</v>
-      </c>
-      <c r="I72" t="n">
-        <v>240</v>
-      </c>
-      <c r="J72" t="n">
-        <v>15</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.21069</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-76.9388</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.22437</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-76.95014</v>
-      </c>
-      <c r="I73" t="n">
-        <v>262</v>
-      </c>
-      <c r="J73" t="n">
-        <v>16</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.22437</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-76.95014</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.21104</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-76.93659</v>
-      </c>
-      <c r="I74" t="n">
-        <v>218</v>
-      </c>
-      <c r="J74" t="n">
-        <v>11</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.21104</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-76.93659</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>ALMIRANTE GUILLERMO BROWN</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.20521</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-76.93652</v>
-      </c>
-      <c r="I75" t="n">
-        <v>226</v>
-      </c>
-      <c r="J75" t="n">
-        <v>20</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.20521</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-76.93652</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>MAX UHLE</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.20637</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-76.96747000000001</v>
-      </c>
-      <c r="I76" t="n">
-        <v>448</v>
-      </c>
-      <c r="J76" t="n">
-        <v>24</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.20637</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-76.96747</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SAN AGUSTIN DE VILLA</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.19737</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-76.95012</v>
-      </c>
-      <c r="I77" t="n">
-        <v>210</v>
-      </c>
-      <c r="J77" t="n">
-        <v>8</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.19737</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-76.95012</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>JUVENTUD CIENTIFICA PADUA</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.21354</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-76.94416</v>
-      </c>
-      <c r="I78" t="n">
-        <v>250</v>
-      </c>
-      <c r="J78" t="n">
-        <v>20</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.21354</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-76.94416</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.19957</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-76.94444</v>
-      </c>
-      <c r="I79" t="n">
-        <v>735</v>
-      </c>
-      <c r="J79" t="n">
-        <v>39</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.19957</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-76.94444</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.23192</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-76.93656</v>
-      </c>
-      <c r="I80" t="n">
-        <v>235</v>
-      </c>
-      <c r="J80" t="n">
-        <v>22</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.23192</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-76.93656</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>MI JESUS</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.23153</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-76.94123999999999</v>
-      </c>
-      <c r="I81" t="n">
-        <v>240</v>
-      </c>
-      <c r="J81" t="n">
-        <v>18</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.23153</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-76.94124</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.20098</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-76.94128000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>238</v>
-      </c>
-      <c r="J82" t="n">
-        <v>12</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.20098</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-76.94128</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>LA MERCED</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.21278</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-76.92646999999999</v>
-      </c>
-      <c r="I83" t="n">
-        <v>746</v>
-      </c>
-      <c r="J83" t="n">
-        <v>29</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.21278</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-76.92647</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>AMERICAN SISTEMS</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-12.24156</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-76.92462999999999</v>
-      </c>
-      <c r="I84" t="n">
-        <v>470</v>
-      </c>
-      <c r="J84" t="n">
-        <v>31</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-12.24156</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-76.92463</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>JOSE JESUS</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.20648</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-76.94862000000001</v>
-      </c>
-      <c r="I85" t="n">
-        <v>201</v>
-      </c>
-      <c r="J85" t="n">
-        <v>19</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.20648</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-76.94862</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>JULIO CESAR TELLO DE OASIS</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.23818</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-76.93501000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>474</v>
-      </c>
-      <c r="J86" t="n">
-        <v>33</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.23818</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-76.93501</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>REINO UNIDO BRITANICO</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-12.2105</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-76.94926</v>
-      </c>
-      <c r="I87" t="n">
-        <v>446</v>
-      </c>
-      <c r="J87" t="n">
-        <v>29</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-12.2105</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-76.94926</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>LA MERCED KID</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.21267</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.92818</v>
-      </c>
-      <c r="I88" t="n">
-        <v>214</v>
-      </c>
-      <c r="J88" t="n">
-        <v>17</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.21267</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.92818</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>CASA ABIERTA DE NAZARETH</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.23836</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-76.91907999999999</v>
-      </c>
-      <c r="I89" t="n">
-        <v>688</v>
-      </c>
-      <c r="J89" t="n">
-        <v>32</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.23836</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-76.91908</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>EL MUNDO NUEVO DE VILLA</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.2216</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-76.94977</v>
-      </c>
-      <c r="I90" t="n">
-        <v>223</v>
-      </c>
-      <c r="J90" t="n">
-        <v>14</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.2216</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-76.94977</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>LUDWING VON MISSES</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.19363</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-76.94544999999999</v>
-      </c>
-      <c r="I91" t="n">
-        <v>178</v>
-      </c>
-      <c r="J91" t="n">
-        <v>23</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.19363</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-76.94545</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>DIVINO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.23281</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-76.94112</v>
-      </c>
-      <c r="I92" t="n">
-        <v>151</v>
-      </c>
-      <c r="J92" t="n">
-        <v>13</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.23281</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-76.94112</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>PAMER</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-12.2245</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-76.93313000000001</v>
-      </c>
-      <c r="I93" t="n">
-        <v>443</v>
-      </c>
-      <c r="J93" t="n">
-        <v>27</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-12.2245</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-76.93313</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>ASCENSION SCHOOL UNICACHI</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-12.2013</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-76.96617999999999</v>
-      </c>
-      <c r="I94" t="n">
-        <v>283</v>
-      </c>
-      <c r="J94" t="n">
-        <v>20</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-12.2013</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-76.96618</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>GLOBAL SCHOOL</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-12.21578</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-76.93786</v>
-      </c>
-      <c r="I95" t="n">
-        <v>208</v>
-      </c>
-      <c r="J95" t="n">
-        <v>9</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-12.21578</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-76.93786</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>INNOVA SCHOOLS - VES LADERAS DE VILLA</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.19171</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-76.95950999999999</v>
-      </c>
-      <c r="I96" t="n">
-        <v>710</v>
-      </c>
-      <c r="J96" t="n">
-        <v>32</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.19171</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-76.95951</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.21592</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-76.94815</v>
-      </c>
-      <c r="I97" t="n">
-        <v>547</v>
-      </c>
-      <c r="J97" t="n">
-        <v>39</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.21592</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-76.94815</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>BABY KINDER</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.19404</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-76.95153000000001</v>
-      </c>
-      <c r="I98" t="n">
-        <v>275</v>
-      </c>
-      <c r="J98" t="n">
-        <v>14</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.19404</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-76.95153</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>CALIFORNIA SCHOOL</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.20633</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-76.96983</v>
-      </c>
-      <c r="I99" t="n">
-        <v>208</v>
-      </c>
-      <c r="J99" t="n">
-        <v>21</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.20633</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-76.96983</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>HOUSTON</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.23074</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-76.94776</v>
-      </c>
-      <c r="I100" t="n">
-        <v>329</v>
-      </c>
-      <c r="J100" t="n">
-        <v>28</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.23074</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-76.94776</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-12.23635</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-76.92027</v>
-      </c>
-      <c r="I101" t="n">
-        <v>307</v>
-      </c>
-      <c r="J101" t="n">
-        <v>22</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-12.23635</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-76.92027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>RAINBOW KIDS</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-12.20461</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-76.94607999999999</v>
-      </c>
-      <c r="I102" t="n">
-        <v>333</v>
-      </c>
-      <c r="J102" t="n">
-        <v>9</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-12.20461</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-76.94608</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>MARANATHA</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-12.20759</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-76.95491</v>
-      </c>
-      <c r="I103" t="n">
-        <v>292</v>
-      </c>
-      <c r="J103" t="n">
-        <v>17</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-12.20759</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-76.95491</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>VIRGEN DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-12.23822</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-76.93689000000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>300</v>
-      </c>
-      <c r="J104" t="n">
-        <v>12</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-12.23822</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-76.93689</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>SANTA ROSA PURISIMA</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-12.2282</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-76.93508</v>
-      </c>
-      <c r="I105" t="n">
-        <v>365</v>
-      </c>
-      <c r="J105" t="n">
-        <v>24</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-12.2282</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-76.93508</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>7242 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-12.21428</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-76.92733</v>
-      </c>
-      <c r="I106" t="n">
-        <v>933</v>
-      </c>
-      <c r="J106" t="n">
-        <v>40</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-12.21428</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-76.92733</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>7243 REY JUAN CARLOS DE BORBON</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-12.233138</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-76.91378</v>
-      </c>
-      <c r="I107" t="n">
-        <v>998</v>
-      </c>
-      <c r="J107" t="n">
-        <v>36</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-12.233138</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-76.91378</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>BLAS PASCAL</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-12.2068</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-76.93199</v>
-      </c>
-      <c r="I108" t="n">
-        <v>254</v>
-      </c>
-      <c r="J108" t="n">
-        <v>24</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-12.2068</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-76.93199</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>CORPORACION EDUCATIVA THE HAPPY WORLD OF THE CHILDREN SAC</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-12.19773</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-76.95499</v>
-      </c>
-      <c r="I109" t="n">
-        <v>210</v>
-      </c>
-      <c r="J109" t="n">
-        <v>14</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-12.19773</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-76.95499</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>SAN LORENZO</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-12.22225</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-76.9267</v>
-      </c>
-      <c r="I110" t="n">
-        <v>235</v>
-      </c>
-      <c r="J110" t="n">
-        <v>23</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-12.22225</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-76.9267</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>PERUANO BRITANICO</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-12.21004</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-76.9344</v>
-      </c>
-      <c r="I111" t="n">
-        <v>490</v>
-      </c>
-      <c r="J111" t="n">
-        <v>30</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-12.21004</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-76.9344</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>EL CARMELO DE VILLA</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-12.21835</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-76.94392999999999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>265</v>
-      </c>
-      <c r="J112" t="n">
-        <v>14</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-12.21835</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-76.94393</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>PEREGRINO SCHOOL</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-12.23543</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-76.91934999999999</v>
-      </c>
-      <c r="I113" t="n">
-        <v>651</v>
-      </c>
-      <c r="J113" t="n">
-        <v>38</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-12.23543</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-76.91935</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>SAN GERMAN</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-12.22683</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-76.97349</v>
-      </c>
-      <c r="I114" t="n">
-        <v>258</v>
-      </c>
-      <c r="J114" t="n">
-        <v>25</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-12.22683</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-76.97349</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>INTEGRA COLLEGE</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-12.19733</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-76.95925</v>
-      </c>
-      <c r="I115" t="n">
-        <v>315</v>
-      </c>
-      <c r="J115" t="n">
-        <v>19</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-12.19733</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-76.95925</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>NORDIC INTERNATIONAL SCHOOL</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-12.229</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-76.97329000000001</v>
-      </c>
-      <c r="I116" t="n">
-        <v>278</v>
-      </c>
-      <c r="J116" t="n">
-        <v>32</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-12.229</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-76.97329</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>SACO OLIVEROS DE VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-12.19486</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-76.94847</v>
-      </c>
-      <c r="I117" t="n">
-        <v>1175</v>
-      </c>
-      <c r="J117" t="n">
-        <v>31</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-12.19486</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-76.94847</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>651</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-12.21774</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-76.93546000000001</v>
-      </c>
-      <c r="I118" t="n">
-        <v>246</v>
-      </c>
-      <c r="J118" t="n">
-        <v>11</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-12.21774</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-76.93546</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>AVANTGARD COLLEGE</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-12.2193</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-76.95842</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J119" t="n">
-        <v>59</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-12.2193</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-76.95842</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>URIBE'S SCHOOL</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-12.2039</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-76.94676</v>
-      </c>
-      <c r="I120" t="n">
-        <v>150</v>
-      </c>
-      <c r="J120" t="n">
-        <v>5</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-12.2039</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-76.94676</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>EL ALBA</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-12.21232</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-76.93662999999999</v>
-      </c>
-      <c r="I121" t="n">
-        <v>413</v>
-      </c>
-      <c r="J121" t="n">
-        <v>18</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-12.21232</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-76.93663</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>INNOVA SCHOOLS - VES VALLEJO</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-12.22237</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-76.9567</v>
-      </c>
-      <c r="I122" t="n">
-        <v>766</v>
-      </c>
-      <c r="J122" t="n">
-        <v>49</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-12.22237</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-76.9567</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-12.19446</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-76.94494</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-12.19446</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-76.94494</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>344861</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MONTESSORI DE VILLA</t>
+          <t>MERCEDES CABELLO DE CARBONERA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.2184</t>
+          <t>-12.22478</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.93516</t>
+          <t>-76.93294</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>343512</t>
+          <t>805942</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>517 MIS PEQUEÑITOS ANGELITOS</t>
+          <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.21541</t>
+          <t>-12.19446</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.93717</t>
+          <t>-76.94494</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>343593</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>652 02 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.2286</t>
+          <t>-12.23838</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.92331</t>
+          <t>-76.92429</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>343606</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>558 CASA MONTESSORI</t>
+          <t>652 03 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.2322</t>
+          <t>-12.23834</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.92093</t>
+          <t>-76.91759</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>343550</t>
+          <t>343625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>652 11 PEQUEÑOS QUERUBINES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.21923</t>
+          <t>-12.21539</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.92286</t>
+          <t>-76.94935</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>343588</t>
+          <t>344385</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>JOHN VON NEUMANN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.22285</t>
+          <t>-12.21938</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.9393</t>
+          <t>-76.93037</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>128</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>343593</t>
+          <t>343512</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>652 02 SANTA ROSA DE LIMA</t>
+          <t>517 MIS PEQUEÑITOS ANGELITOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.23838</t>
+          <t>-12.21541</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.92429</t>
+          <t>-76.93717</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>343606</t>
+          <t>345403</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>652 03 SAN MARTIN DE PORRES</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.23834</t>
+          <t>-12.21104</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.91759</t>
+          <t>-76.93659</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>343625</t>
+          <t>804075</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>652 11 PEQUEÑOS QUERUBINES</t>
+          <t>651</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.21539</t>
+          <t>-12.21774</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.94935</t>
+          <t>-76.93546</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>343630</t>
+          <t>346049</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>652 10</t>
+          <t>NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.1913</t>
+          <t>-12.20098</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.94121</t>
+          <t>-76.94128</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>343673</t>
+          <t>687241</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>652-17 CAPULLITO</t>
+          <t>VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.22614</t>
+          <t>-12.23822</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.9205</t>
+          <t>-76.93689</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>343692</t>
+          <t>343545</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>652 22 SEÑOR DE LOS MILAGROS</t>
+          <t>558 CASA MONTESSORI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.20616</t>
+          <t>-12.2322</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.95102</t>
+          <t>-76.92093</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>343710</t>
+          <t>591050</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>652 24 / 7232 DANIEL ALCIDES CARRION</t>
+          <t>DIVINO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.21488</t>
+          <t>-12.23281</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.95469</t>
+          <t>-76.94112</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>343791</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6004 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>6066 VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.19548</t>
+          <t>-12.21334</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.96105</t>
+          <t>-76.93987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>343767</t>
+          <t>343913</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6063 JOSE CARLOS MARIATEGUI</t>
+          <t>7090 FORJADORES DEL PERU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.20085</t>
+          <t>-12.19227</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.94336</t>
+          <t>-76.94151</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>343772</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6064 FRANCISCO BOLOGNESI</t>
+          <t>MI DULCE JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.21011</t>
+          <t>-12.22169</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.93622</t>
+          <t>-76.94446</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>343786</t>
+          <t>345120</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6065 PERU INGLATERRA</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.2076</t>
+          <t>-12.22297</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.9419</t>
+          <t>-76.94142</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>343791</t>
+          <t>536407</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6066 VILLA EL SALVADOR</t>
+          <t>EL MUNDO NUEVO DE VILLA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.21334</t>
+          <t>-12.2216</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.93987</t>
+          <t>-76.94977</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>343809</t>
+          <t>648891</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6067 JUAN VELASCO ALVARADO</t>
+          <t>BABY KINDER</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.2244361218332</t>
+          <t>-12.19404</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.9282762820025</t>
+          <t>-76.95153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>343814</t>
+          <t>688410</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6068 MANUEL GONZALES PRADA</t>
+          <t>CORPORACION EDUCATIVA THE HAPPY WORLD OF THE CHILDREN SAC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.22581</t>
+          <t>-12.19773</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.93209</t>
+          <t>-76.95499</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>343828</t>
+          <t>689160</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6069 PACHACUTEC</t>
+          <t>EL CARMELO DE VILLA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.21846</t>
+          <t>-12.21835</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.93606</t>
+          <t>-76.94393</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>343847</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>MONTESSORI DE VILLA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.2239</t>
+          <t>-12.2184</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.94643</t>
+          <t>-76.93516</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>343852</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6076 REPUBLICA DE NICARAGUA</t>
+          <t>557</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.2201</t>
+          <t>-12.2286</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.93966</t>
+          <t>-76.92331</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>343871</t>
+          <t>343550</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.21089</t>
+          <t>-12.21923</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.9536</t>
+          <t>-76.92286</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>343588</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7077 VIRGEN DEL CARMEN</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.21796</t>
+          <t>-12.22285</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.96735</t>
+          <t>-76.9393</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>363</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>345002</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7084 PERUANO SUIZO</t>
+          <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.22934</t>
+          <t>-12.19373</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.92323</t>
+          <t>-76.96148</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>343913</t>
+          <t>345177</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7090 FORJADORES DEL PERU</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.19227</t>
+          <t>-12.21069</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.94151</t>
+          <t>-76.9388</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>343927</t>
+          <t>345257</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7091 REPUBLICA DEL PERU</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.22856</t>
+          <t>-12.22437</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.94364</t>
+          <t>-76.95014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>343932</t>
+          <t>343630</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7092 JUAN PABLO II</t>
+          <t>652 10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.18848</t>
+          <t>-12.1913</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.94866</t>
+          <t>-76.94121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>343946</t>
+          <t>343673</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7093 REPUBLICA DE FRANCIA</t>
+          <t>652-17 CAPULLITO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.2293</t>
+          <t>-12.22614</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.93405</t>
+          <t>-76.9205</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>345101</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7094 SASAKAWA</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO DE VILLA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.20551</t>
+          <t>-12.24192</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.95434</t>
+          <t>-76.92701</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>343965</t>
+          <t>345163</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7095 PERU ITALIA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.19393</t>
+          <t>-12.19354</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.95851</t>
+          <t>-76.95428</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>343989</t>
+          <t>346209</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7097 VILLA AMSTELVEEN</t>
+          <t>LA MERCED KID</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.21664</t>
+          <t>-12.21267</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.93278</t>
+          <t>-76.92818</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,42 +2609,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>687199</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7215 NACIONES UNIDAS</t>
+          <t>MARANATHA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.2369</t>
+          <t>-12.20759</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.92089</t>
+          <t>-76.95491</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>344012</t>
+          <t>344130</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.19661</t>
+          <t>-12.21623</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.96223</t>
+          <t>-76.9305</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>344026</t>
+          <t>344229</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>REPUBLICA DE BOLIVIA</t>
+          <t>BENJAMIN FRANKLIN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.19653</t>
+          <t>-12.22252</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.94983</t>
+          <t>-76.92629</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>198</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>344031</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.23982</t>
+          <t>-12.22194</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.91742</t>
+          <t>-76.92251</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>344045</t>
+          <t>344644</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7228 PERUANO CANADIENSE</t>
+          <t>PATRON SANTIAGO DE YANACA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.23977</t>
+          <t>-12.2225</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.92488</t>
+          <t>-76.95098</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>344088</t>
+          <t>346030</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>7234 / 7234 LAS PALMERAS</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.248</t>
+          <t>-12.23153</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.93124</t>
+          <t>-76.94124</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>344111</t>
+          <t>848550</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7237 PERU VALLADOLID</t>
+          <t>EL ALBA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.24054</t>
+          <t>-12.21232</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.93255</t>
+          <t>-76.93663</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>413</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>344125</t>
+          <t>344470</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7236 MAX UHLE</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.24546</t>
+          <t>-12.19282</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.91862</t>
+          <t>-76.95905</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>344130</t>
+          <t>344724</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
+          <t>SEBASTIAN LORENTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.21623</t>
+          <t>-12.23022</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.9305</t>
+          <t>-76.94175</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>344149</t>
+          <t>346092</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
+          <t>JOSE JESUS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.23802</t>
+          <t>-12.20648</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.93899</t>
+          <t>-76.94862</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>344154</t>
+          <t>782691</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>7240 JESUS DE NAZARETH</t>
+          <t>INTEGRA COLLEGE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.24413</t>
+          <t>-12.19733</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.92919</t>
+          <t>-76.95925</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>344168</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>HANS CHRISTIAN ANDERSEN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.24311</t>
+          <t>-12.21006</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.94398</t>
+          <t>-76.9396</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>344173</t>
+          <t>345021</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ADVENTISTA SALVADOR</t>
+          <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.19922</t>
+          <t>-12.20411</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.95228</t>
+          <t>-76.94568</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>344192</t>
+          <t>345460</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BARTOLOME HERRERA</t>
+          <t>ALMIRANTE GUILLERMO BROWN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.19965</t>
+          <t>-12.20521</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.95051</t>
+          <t>-76.93652</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>344229</t>
+          <t>345714</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BENJAMIN FRANKLIN</t>
+          <t>JUVENTUD CIENTIFICA PADUA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.22252</t>
+          <t>-12.21354</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.92629</t>
+          <t>-76.94416</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>344286</t>
+          <t>597660</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CRISTO REY DE VILLA</t>
+          <t>ASCENSION SCHOOL UNICACHI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.20437</t>
+          <t>-12.2013</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.93648</t>
+          <t>-76.96618</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>344291</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EL DIVINO MAESTRO</t>
+          <t>7077 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.23037</t>
+          <t>-12.21796</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.92559</t>
+          <t>-76.96735</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>649739</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>CALIFORNIA SCHOOL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.22194</t>
+          <t>-12.20633</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.92251</t>
+          <t>-76.96983</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>343692</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HANS CHRISTIAN ANDERSEN</t>
+          <t>652 22 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.21006</t>
+          <t>-12.20616</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.9396</t>
+          <t>-76.95102</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>506</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,42 +3787,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>344385</t>
+          <t>344578</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JOHN VON NEUMANN</t>
+          <t>MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.21938</t>
+          <t>-12.23934</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.93037</t>
+          <t>-76.92321</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>344470</t>
+          <t>345865</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.19282</t>
+          <t>-12.23192</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.95905</t>
+          <t>-76.93656</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>344559</t>
+          <t>686699</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.22566</t>
+          <t>-12.23635</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.94213</t>
+          <t>-76.92027</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>344578</t>
+          <t>559470</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA CONCEPCION</t>
+          <t>LUDWING VON MISSES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.23934</t>
+          <t>-12.19363</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.92321</t>
+          <t>-76.94545</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>178</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>344620</t>
+          <t>688919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>SAN LORENZO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.2019</t>
+          <t>-12.22225</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.95481</t>
+          <t>-76.9267</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>344644</t>
+          <t>344012</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PATRON SANTIAGO DE YANACA</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.2225</t>
+          <t>-12.19661</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.95098</t>
+          <t>-76.96223</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>603</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>345648</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SEBASTIAN LORENTE</t>
+          <t>MAX UHLE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.23022</t>
+          <t>-12.20637</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.94175</t>
+          <t>-76.96747</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>344781</t>
+          <t>687255</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>SANTA ROSA PURISIMA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.22662</t>
+          <t>-12.2282</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.92649</t>
+          <t>-76.93508</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>344861</t>
+          <t>688349</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MERCEDES CABELLO DE CARBONERA</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.22478</t>
+          <t>-12.2068</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.93294</t>
+          <t>-76.93199</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>344875</t>
+          <t>343932</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PROLOG DE VILLA EL SALVADOR</t>
+          <t>7092 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.22776</t>
+          <t>-12.18848</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.92756</t>
+          <t>-76.94866</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>344291</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HIPOLITO UNANUE</t>
+          <t>EL DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.21541</t>
+          <t>-12.23037</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.94492</t>
+          <t>-76.92559</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>345002</t>
+          <t>733634</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMANN</t>
+          <t>SAN GERMAN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.19373</t>
+          <t>-12.22683</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.96148</t>
+          <t>-76.97349</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>345021</t>
+          <t>343965</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JUAN ESPINOZA MEDRANO</t>
+          <t>7095 PERU ITALIA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.20411</t>
+          <t>-12.19393</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.94568</t>
+          <t>-76.95851</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,42 +4593,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>345097</t>
+          <t>344007</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MI DULCE JESUS</t>
+          <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.22169</t>
+          <t>-12.2369</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.94446</t>
+          <t>-76.92089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>646</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>591074</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO DE VILLA</t>
+          <t>PAMER</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.24192</t>
+          <t>-12.2245</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.92701</t>
+          <t>-76.93313</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>345120</t>
+          <t>686595</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.22297</t>
+          <t>-12.23074</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.94142</t>
+          <t>-76.94776</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>345163</t>
+          <t>343710</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>652 24 / 7232 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.19354</t>
+          <t>-12.21488</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.95428</t>
+          <t>-76.95469</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>522</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>345177</t>
+          <t>344559</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.21069</t>
+          <t>-12.22566</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.9388</t>
+          <t>-76.94213</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>345257</t>
+          <t>346068</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>LA MERCED</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.22437</t>
+          <t>-12.21278</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.95014</t>
+          <t>-76.92647</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>746</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>345403</t>
+          <t>346153</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>REINO UNIDO BRITANICO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.21104</t>
+          <t>-12.2105</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.93659</t>
+          <t>-76.94926</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>345460</t>
+          <t>344088</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ALMIRANTE GUILLERMO BROWN</t>
+          <t>7234 / 7234 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.20521</t>
+          <t>-12.248</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.93652</t>
+          <t>-76.93124</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>593</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>345648</t>
+          <t>344173</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MAX UHLE</t>
+          <t>ADVENTISTA SALVADOR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.20637</t>
+          <t>-12.19922</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.96747</t>
+          <t>-76.95228</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>467</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>345709</t>
+          <t>344286</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE VILLA</t>
+          <t>CRISTO REY DE VILLA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.19737</t>
+          <t>-12.20437</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.95012</t>
+          <t>-76.93648</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>345714</t>
+          <t>689117</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JUVENTUD CIENTIFICA PADUA</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.21354</t>
+          <t>-12.21004</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.94416</t>
+          <t>-76.9344</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>345832</t>
+          <t>346087</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>AMERICAN SISTEMS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.19957</t>
+          <t>-12.24156</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.94444</t>
+          <t>-76.92463</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>345865</t>
+          <t>783488</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>SACO OLIVEROS DE VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.23192</t>
+          <t>-12.19486</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.93656</t>
+          <t>-76.94847</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>346030</t>
+          <t>522778</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>CASA ABIERTA DE NAZARETH</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.23153</t>
+          <t>-12.23836</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.94124</t>
+          <t>-76.91908</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>688</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>623452</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NUESTRO SEÑOR DE LA MISERICORDIA</t>
+          <t>INNOVA SCHOOLS - VES LADERAS DE VILLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.20098</t>
+          <t>-12.19171</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.94128</t>
+          <t>-76.95951</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>346068</t>
+          <t>783407</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LA MERCED</t>
+          <t>NORDIC INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.21278</t>
+          <t>-12.229</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.92647</t>
+          <t>-76.97329</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>346087</t>
+          <t>343989</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AMERICAN SISTEMS</t>
+          <t>7097 VILLA AMSTELVEEN</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.24156</t>
+          <t>-12.21664</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.92463</t>
+          <t>-76.93278</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>782</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>346092</t>
+          <t>346105</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JOSE JESUS</t>
+          <t>JULIO CESAR TELLO DE OASIS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.20648</t>
+          <t>-12.23818</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.94862</t>
+          <t>-76.93501</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>346105</t>
+          <t>344960</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JULIO CESAR TELLO DE OASIS</t>
+          <t>HIPOLITO UNANUE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.23818</t>
+          <t>-12.21541</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.93501</t>
+          <t>-76.94492</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>346153</t>
+          <t>687585</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>REINO UNIDO BRITANICO</t>
+          <t>7243 REY JUAN CARLOS DE BORBON</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.2105</t>
+          <t>-12.233138</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.94926</t>
+          <t>-76.91378</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>998</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>346209</t>
+          <t>689216</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LA MERCED KID</t>
+          <t>PEREGRINO SCHOOL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.21267</t>
+          <t>-12.23543</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.92818</t>
+          <t>-76.91935</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>651</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>522778</t>
+          <t>345832</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CASA ABIERTA DE NAZARETH</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.23836</t>
+          <t>-12.19957</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.91908</t>
+          <t>-76.94444</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>735</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>536407</t>
+          <t>625007</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EL MUNDO NUEVO DE VILLA</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.2216</t>
+          <t>-12.21592</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.94977</t>
+          <t>-76.94815</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>559470</t>
+          <t>687383</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LUDWING VON MISSES</t>
+          <t>7242 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.19363</t>
+          <t>-12.21428</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.94545</t>
+          <t>-76.92733</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>933</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,42 +6081,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>591050</t>
+          <t>344149</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS</t>
+          <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.23281</t>
+          <t>-12.23802</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.94112</t>
+          <t>-76.93899</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>915</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>591074</t>
+          <t>344620</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PAMER</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.2245</t>
+          <t>-12.2019</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.93313</t>
+          <t>-76.95481</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>753</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>597660</t>
+          <t>344154</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ASCENSION SCHOOL UNICACHI</t>
+          <t>7240 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.2013</t>
+          <t>-12.24413</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.96618</t>
+          <t>-76.92919</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>616197</t>
+          <t>854310</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GLOBAL SCHOOL</t>
+          <t>INNOVA SCHOOLS - VES VALLEJO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.21578</t>
+          <t>-12.22237</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.93786</t>
+          <t>-76.9567</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>766</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>623452</t>
+          <t>837127</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VES LADERAS DE VILLA</t>
+          <t>URIBE'S SCHOOL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.19171</t>
+          <t>-12.2039</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.95951</t>
+          <t>-76.94676</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>625007</t>
+          <t>344875</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>PROLOG DE VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.21592</t>
+          <t>-12.22776</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.94815</t>
+          <t>-76.92756</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>946</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>648891</t>
+          <t>344031</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BABY KINDER</t>
+          <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.19404</t>
+          <t>-12.23982</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.95153</t>
+          <t>-76.91742</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>649739</t>
+          <t>344125</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CALIFORNIA SCHOOL</t>
+          <t>7236 MAX UHLE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.20633</t>
+          <t>-12.24546</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.96983</t>
+          <t>-76.91862</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>846</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>686595</t>
+          <t>343852</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HOUSTON</t>
+          <t>6076 REPUBLICA DE NICARAGUA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.23074</t>
+          <t>-12.2201</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.94776</t>
+          <t>-76.93966</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,42 +6639,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>686699</t>
+          <t>343809</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>7215 NACIONES UNIDAS</t>
+          <t>6067 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.23635</t>
+          <t>-12.2244361218332</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-76.92027</t>
+          <t>-76.9282762820025</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>686760</t>
+          <t>344111</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RAINBOW KIDS</t>
+          <t>7237 PERU VALLADOLID</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.20461</t>
+          <t>-12.24054</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-76.94608</t>
+          <t>-76.93255</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>687199</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MARANATHA</t>
+          <t>AVANTGARD COLLEGE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.20759</t>
+          <t>-12.2193</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.95491</t>
+          <t>-76.95842</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6825,42 +6825,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>687241</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VIRGEN DEL ROSARIO</t>
+          <t>6004 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.23822</t>
+          <t>-12.19548</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-76.93689</t>
+          <t>-76.96105</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>687255</t>
+          <t>343871</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SANTA ROSA PURISIMA</t>
+          <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.2282</t>
+          <t>-12.21089</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.93508</t>
+          <t>-76.9536</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>687383</t>
+          <t>343946</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>7242 DIVINO MAESTRO</t>
+          <t>7093 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.21428</t>
+          <t>-12.2293</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-76.92733</t>
+          <t>-76.93405</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>687585</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7243 REY JUAN CARLOS DE BORBON</t>
+          <t>7094 SASAKAWA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.233138</t>
+          <t>-12.20551</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-76.91378</t>
+          <t>-76.95434</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>688349</t>
+          <t>343786</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>6065 PERU INGLATERRA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.2068</t>
+          <t>-12.2076</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-76.93199</t>
+          <t>-76.9419</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>688410</t>
+          <t>343767</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CORPORACION EDUCATIVA THE HAPPY WORLD OF THE CHILDREN SAC</t>
+          <t>6063 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.19773</t>
+          <t>-12.20085</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-76.95499</t>
+          <t>-76.94336</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>688919</t>
+          <t>343772</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SAN LORENZO</t>
+          <t>6064 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.22225</t>
+          <t>-12.21011</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-76.9267</t>
+          <t>-76.93622</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>689117</t>
+          <t>343828</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>6069 PACHACUTEC</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.21004</t>
+          <t>-12.21846</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-76.9344</t>
+          <t>-76.93606</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>689160</t>
+          <t>343927</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EL CARMELO DE VILLA</t>
+          <t>7091 REPUBLICA DEL PERU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-12.21835</t>
+          <t>-12.22856</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-76.94393</t>
+          <t>-76.94364</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>689216</t>
+          <t>344781</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PEREGRINO SCHOOL</t>
+          <t>VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.23543</t>
+          <t>-12.22662</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-76.91935</t>
+          <t>-76.92649</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>733634</t>
+          <t>345709</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SAN GERMAN</t>
+          <t>SAN AGUSTIN DE VILLA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.22683</t>
+          <t>-12.19737</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-76.97349</t>
+          <t>-76.95012</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>782691</t>
+          <t>343814</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>INTEGRA COLLEGE</t>
+          <t>6068 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.19733</t>
+          <t>-12.22581</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-76.95925</t>
+          <t>-76.93209</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>783407</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NORDIC INTERNATIONAL SCHOOL</t>
+          <t>7084 PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.229</t>
+          <t>-12.22934</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-76.97329</t>
+          <t>-76.92323</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>783488</t>
+          <t>344045</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE VILLA EL SALVADOR</t>
+          <t>7228 PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.19486</t>
+          <t>-12.23977</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-76.94847</t>
+          <t>-76.92488</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>804075</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.21774</t>
+          <t>-12.24311</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-76.93546</t>
+          <t>-76.94398</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>828972</t>
+          <t>344192</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AVANTGARD COLLEGE</t>
+          <t>BARTOLOME HERRERA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.2193</t>
+          <t>-12.19965</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-76.95842</t>
+          <t>-76.95051</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>837127</t>
+          <t>616197</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>URIBE'S SCHOOL</t>
+          <t>GLOBAL SCHOOL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.2039</t>
+          <t>-12.21578</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-76.94676</t>
+          <t>-76.93786</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>848550</t>
+          <t>686760</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>EL ALBA</t>
+          <t>RAINBOW KIDS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.21232</t>
+          <t>-12.20461</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-76.93663</t>
+          <t>-76.94608</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>854310</t>
+          <t>344026</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VES VALLEJO</t>
+          <t>REPUBLICA DE BOLIVIA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.22237</t>
+          <t>-12.19653</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-76.9567</t>
+          <t>-76.94983</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>805942</t>
+          <t>343847</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
+          <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.19446</t>
+          <t>-12.2239</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-76.94494</t>
+          <t>-76.94643</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>344861</t>
+          <t>854310</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MERCEDES CABELLO DE CARBONERA</t>
+          <t>INNOVA SCHOOLS - VES VALLEJO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.22478</t>
+          <t>766</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.93294</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.22237</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-76.9567</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>805942</t>
+          <t>848550</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
+          <t>EL ALBA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.19446</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.94494</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.21232</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-76.93663</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>343526</t>
+          <t>837127</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>526 SANTISIMA VIRGEN DEL PERPETUO SOCORRO</t>
+          <t>URIBE'S SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.21002</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.9401</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-12.2039</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.94676</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>343593</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>652 02 SANTA ROSA DE LIMA</t>
+          <t>AVANTGARD COLLEGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.23838</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.92429</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-12.2193</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.95842</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>343606</t>
+          <t>805942</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>652 03 SAN MARTIN DE PORRES</t>
+          <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.23834</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.91759</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-12.19446</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.94494</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>343625</t>
+          <t>804075</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>652 11 PEQUEÑOS QUERUBINES</t>
+          <t>651</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.21539</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.94935</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-12.21774</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.93546</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>344385</t>
+          <t>783488</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JOHN VON NEUMANN</t>
+          <t>SACO OLIVEROS DE VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.21938</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.93037</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-12.19486</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.94847</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>343512</t>
+          <t>783407</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>517 MIS PEQUEÑITOS ANGELITOS</t>
+          <t>NORDIC INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.21541</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.93717</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-12.229</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.97329</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>345403</t>
+          <t>782691</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>INTEGRA COLLEGE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.21104</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.93659</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.19733</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.95925</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>804075</t>
+          <t>733634</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>SAN GERMAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.21774</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.93546</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-12.22683</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.97349</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>689216</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NUESTRO SEÑOR DE LA MISERICORDIA</t>
+          <t>PEREGRINO SCHOOL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.20098</t>
+          <t>651</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.94128</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.23543</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.91935</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>687241</t>
+          <t>689160</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VIRGEN DEL ROSARIO</t>
+          <t>EL CARMELO DE VILLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.23822</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.93689</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-12.21835</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.94393</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>689117</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>558 CASA MONTESSORI</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.2322</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.92093</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-12.21004</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.9344</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,42 +1307,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>591050</t>
+          <t>688919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS</t>
+          <t>SAN LORENZO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.23281</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.94112</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-12.22225</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.9267</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>343791</t>
+          <t>688410</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6066 VILLA EL SALVADOR</t>
+          <t>CORPORACION EDUCATIVA THE HAPPY WORLD OF THE CHILDREN SAC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.21334</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.93987</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>-12.19773</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>-76.95499</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>343913</t>
+          <t>688349</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7090 FORJADORES DEL PERU</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.19227</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.94151</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-12.2068</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93199</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>345097</t>
+          <t>687585</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MI DULCE JESUS</t>
+          <t>7243 REY JUAN CARLOS DE BORBON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.22169</t>
+          <t>998</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.94446</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.233138</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.91378</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>345120</t>
+          <t>687383</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>7242 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.22297</t>
+          <t>933</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.94142</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.21428</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.92733</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>536407</t>
+          <t>687255</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EL MUNDO NUEVO DE VILLA</t>
+          <t>SANTA ROSA PURISIMA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.2216</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.94977</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-12.2282</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93508</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>648891</t>
+          <t>687241</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BABY KINDER</t>
+          <t>VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.19404</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.95153</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-12.23822</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93689</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>688410</t>
+          <t>687199</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CORPORACION EDUCATIVA THE HAPPY WORLD OF THE CHILDREN SAC</t>
+          <t>MARANATHA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.19773</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.95499</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.20759</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.95491</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>689160</t>
+          <t>686760</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EL CARMELO DE VILLA</t>
+          <t>RAINBOW KIDS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.21835</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.94393</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-12.20461</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.94608</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>686699</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MONTESSORI DE VILLA</t>
+          <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.2184</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.93516</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-12.23635</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.92027</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>686595</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.2286</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.92331</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-12.23074</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.94776</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>343550</t>
+          <t>649739</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>CALIFORNIA SCHOOL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.21923</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.92286</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.20633</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.96983</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>343588</t>
+          <t>648891</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>BABY KINDER</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.22285</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.9393</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>-12.19404</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.95153</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>345002</t>
+          <t>625007</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMANN</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.19373</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.96148</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>-12.21592</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.94815</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>345177</t>
+          <t>623452</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>INNOVA SCHOOLS - VES LADERAS DE VILLA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.21069</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.9388</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.19171</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.95951</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>345257</t>
+          <t>616197</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>GLOBAL SCHOOL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.22437</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.95014</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-12.21578</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.93786</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>343630</t>
+          <t>597660</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>652 10</t>
+          <t>ASCENSION SCHOOL UNICACHI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.1913</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.94121</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-12.2013</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.96618</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,42 +2361,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>343673</t>
+          <t>591074</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>652-17 CAPULLITO</t>
+          <t>PAMER</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.22614</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.9205</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-12.2245</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.93313</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>591050</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO DE VILLA</t>
+          <t>DIVINO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.24192</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.92701</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-12.23281</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.94112</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>345163</t>
+          <t>559470</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>LUDWING VON MISSES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.19354</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.95428</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.19363</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.94545</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>346209</t>
+          <t>536407</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LA MERCED KID</t>
+          <t>EL MUNDO NUEVO DE VILLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.21267</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.92818</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-12.2216</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.94977</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>687199</t>
+          <t>522778</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MARANATHA</t>
+          <t>CASA ABIERTA DE NAZARETH</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.20759</t>
+          <t>688</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.95491</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-12.23836</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.91908</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>344130</t>
+          <t>346209</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
+          <t>LA MERCED KID</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.21623</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.9305</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-12.21267</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.92818</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>344229</t>
+          <t>346153</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BENJAMIN FRANKLIN</t>
+          <t>REINO UNIDO BRITANICO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.22252</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.92629</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>-12.2105</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.94926</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>346105</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>JULIO CESAR TELLO DE OASIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.22194</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.92251</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-12.23818</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.93501</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>344644</t>
+          <t>346092</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PATRON SANTIAGO DE YANACA</t>
+          <t>JOSE JESUS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.2225</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.95098</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-12.20648</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.94862</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>346030</t>
+          <t>346087</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>AMERICAN SISTEMS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.23153</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.94124</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.24156</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.92463</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>848550</t>
+          <t>346068</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL ALBA</t>
+          <t>LA MERCED</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.21232</t>
+          <t>746</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.93663</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>-12.21278</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.92647</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>344470</t>
+          <t>346049</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.19282</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.95905</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.20098</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.94128</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>346030</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SEBASTIAN LORENTE</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.23022</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.94175</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.23153</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.94124</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>346092</t>
+          <t>345865</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JOSE JESUS</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.20648</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.94862</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-12.23192</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.93656</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>782691</t>
+          <t>345832</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INTEGRA COLLEGE</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.19733</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.95925</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-12.19957</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.94444</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,42 +3291,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>345714</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HANS CHRISTIAN ANDERSEN</t>
+          <t>JUVENTUD CIENTIFICA PADUA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.21006</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.9396</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-12.21354</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.94416</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>345021</t>
+          <t>345709</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JUAN ESPINOZA MEDRANO</t>
+          <t>SAN AGUSTIN DE VILLA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.20411</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.94568</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-12.19737</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.95012</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>345460</t>
+          <t>345648</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ALMIRANTE GUILLERMO BROWN</t>
+          <t>MAX UHLE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.20521</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.93652</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.20637</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.96747</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>345714</t>
+          <t>345460</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JUVENTUD CIENTIFICA PADUA</t>
+          <t>ALMIRANTE GUILLERMO BROWN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.21354</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.94416</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.20521</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.93652</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>597660</t>
+          <t>345403</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ASCENSION SCHOOL UNICACHI</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.2013</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.96618</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-12.21104</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.93659</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>345257</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>7077 VIRGEN DEL CARMEN</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.21796</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.96735</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-12.22437</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.95014</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>649739</t>
+          <t>345177</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CALIFORNIA SCHOOL</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.20633</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.96983</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-12.21069</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.9388</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>343692</t>
+          <t>345163</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>652 22 SEÑOR DE LOS MILAGROS</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.20616</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.95102</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>-12.19354</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.95428</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>344578</t>
+          <t>345120</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA CONCEPCION</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.23934</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.92321</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-12.22297</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.94142</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>345865</t>
+          <t>345101</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO DE VILLA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.23192</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.93656</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-12.24192</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.92701</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>686699</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>7215 NACIONES UNIDAS</t>
+          <t>MI DULCE JESUS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.23635</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.92027</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-12.22169</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.94446</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>559470</t>
+          <t>345021</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LUDWING VON MISSES</t>
+          <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.19363</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.94545</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>-12.20411</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.94568</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,42 +4035,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>688919</t>
+          <t>345002</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAN LORENZO</t>
+          <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.22225</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.9267</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-12.19373</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.96148</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>344012</t>
+          <t>344960</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>HIPOLITO UNANUE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.19661</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.96223</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>-12.21541</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.94492</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>345648</t>
+          <t>344875</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MAX UHLE</t>
+          <t>PROLOG DE VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.20637</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.96747</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-12.22776</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.92756</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>687255</t>
+          <t>344861</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SANTA ROSA PURISIMA</t>
+          <t>MERCEDES CABELLO DE CARBONERA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.2282</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.93508</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-12.22478</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.93294</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>688349</t>
+          <t>344781</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.2068</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.93199</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-12.22662</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.92649</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>343932</t>
+          <t>344724</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>7092 JUAN PABLO II</t>
+          <t>SEBASTIAN LORENTE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.18848</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.94866</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-12.23022</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.94175</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>344291</t>
+          <t>344644</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EL DIVINO MAESTRO</t>
+          <t>PATRON SANTIAGO DE YANACA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.23037</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.92559</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-12.2225</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.95098</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>733634</t>
+          <t>344620</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN GERMAN</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.22683</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.97349</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-12.2019</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.95481</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>343965</t>
+          <t>344578</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7095 PERU ITALIA</t>
+          <t>MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.19393</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.95851</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-12.23934</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.92321</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,42 +4593,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>344559</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>7215 NACIONES UNIDAS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.2369</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.92089</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>-12.22566</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.94213</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>591074</t>
+          <t>344470</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PAMER</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.2245</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.93313</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-12.19282</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.95905</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>686595</t>
+          <t>344385</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HOUSTON</t>
+          <t>JOHN VON NEUMANN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.23074</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.94776</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-12.21938</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.93037</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>343710</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>652 24 / 7232 DANIEL ALCIDES CARRION</t>
+          <t>HANS CHRISTIAN ANDERSEN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.21488</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.95469</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>-12.21006</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.9396</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>344559</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.22566</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.94213</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-12.22194</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.92251</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>346068</t>
+          <t>344291</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LA MERCED</t>
+          <t>EL DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.21278</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.92647</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>-12.23037</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.92559</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>346153</t>
+          <t>344286</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>REINO UNIDO BRITANICO</t>
+          <t>CRISTO REY DE VILLA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.2105</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.94926</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-12.20437</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.93648</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>344088</t>
+          <t>344229</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>7234 / 7234 LAS PALMERAS</t>
+          <t>BENJAMIN FRANKLIN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.248</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.93124</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>-12.22252</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.92629</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>344173</t>
+          <t>344192</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADVENTISTA SALVADOR</t>
+          <t>BARTOLOME HERRERA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.19922</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.95228</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>-12.19965</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.95051</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>344286</t>
+          <t>344173</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CRISTO REY DE VILLA</t>
+          <t>ADVENTISTA SALVADOR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.20437</t>
+          <t>467</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.93648</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-12.19922</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.95228</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>689117</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.21004</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.9344</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>-12.24311</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.94398</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>346087</t>
+          <t>344154</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AMERICAN SISTEMS</t>
+          <t>7240 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.24156</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.92463</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>-12.24413</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.92919</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>783488</t>
+          <t>344149</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE VILLA EL SALVADOR</t>
+          <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.19486</t>
+          <t>915</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.94847</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>-12.23802</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.93899</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>522778</t>
+          <t>344130</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CASA ABIERTA DE NAZARETH</t>
+          <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.23836</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.91908</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>-12.21623</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.9305</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>623452</t>
+          <t>344125</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VES LADERAS DE VILLA</t>
+          <t>7236 MAX UHLE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.19171</t>
+          <t>846</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.95951</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>-12.24546</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.91862</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>783407</t>
+          <t>344111</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NORDIC INTERNATIONAL SCHOOL</t>
+          <t>7237 PERU VALLADOLID</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.229</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.97329</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-12.24054</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.93255</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>343989</t>
+          <t>344088</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7097 VILLA AMSTELVEEN</t>
+          <t>7234 / 7234 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.21664</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.93278</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>-12.248</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.93124</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>346105</t>
+          <t>344045</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JULIO CESAR TELLO DE OASIS</t>
+          <t>7228 PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.23818</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.93501</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-12.23977</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.92488</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>344031</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIPOLITO UNANUE</t>
+          <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.21541</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.94492</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-12.23982</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.91742</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>687585</t>
+          <t>344026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>7243 REY JUAN CARLOS DE BORBON</t>
+          <t>REPUBLICA DE BOLIVIA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.233138</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.91378</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>-12.19653</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-76.94983</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>689216</t>
+          <t>344012</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PEREGRINO SCHOOL</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.23543</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.91935</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>-12.19661</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.96223</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,42 +5895,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>345832</t>
+          <t>344007</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.19957</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.94444</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>-12.2369</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.92089</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>625007</t>
+          <t>343989</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>7097 VILLA AMSTELVEEN</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.21592</t>
+          <t>782</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.94815</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-12.21664</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.93278</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>687383</t>
+          <t>343965</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>7242 DIVINO MAESTRO</t>
+          <t>7095 PERU ITALIA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.21428</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.92733</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>-12.19393</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.95851</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>344149</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
+          <t>7094 SASAKAWA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.23802</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.93899</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>-12.20551</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.95434</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>344620</t>
+          <t>343946</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>7093 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.2019</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.95481</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>-12.2293</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.93405</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>344154</t>
+          <t>343932</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>7240 JESUS DE NAZARETH</t>
+          <t>7092 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.24413</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.92919</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>-12.18848</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.94866</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>854310</t>
+          <t>343927</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VES VALLEJO</t>
+          <t>7091 REPUBLICA DEL PERU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.22237</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.9567</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>-12.22856</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-76.94364</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>837127</t>
+          <t>343913</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>URIBE'S SCHOOL</t>
+          <t>7090 FORJADORES DEL PERU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.2039</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.94676</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>-12.19227</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.94151</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>344875</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PROLOG DE VILLA EL SALVADOR</t>
+          <t>7084 PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.22776</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.92756</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>-12.22934</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.92323</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>344031</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
+          <t>7077 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.23982</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.91742</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-12.21796</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-76.96735</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>344125</t>
+          <t>343871</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>7236 MAX UHLE</t>
+          <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.24546</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.91862</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>-12.21089</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-76.9536</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6587,22 +6587,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>-12.2201</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>-76.93966</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>343809</t>
+          <t>343847</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>6067 JUAN VELASCO ALVARADO</t>
+          <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.2244361218332</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-76.9282762820025</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>-12.2239</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.94643</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>344111</t>
+          <t>343828</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>7237 PERU VALLADOLID</t>
+          <t>6069 PACHACUTEC</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.24054</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-76.93255</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>-12.21846</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.93606</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>828972</t>
+          <t>343814</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AVANTGARD COLLEGE</t>
+          <t>6068 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.2193</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.95842</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>-12.22581</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.93209</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,37 +6825,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>343809</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>6004 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>6067 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.19548</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-76.96105</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>-12.2244361218332</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.9282762820025</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>343871</t>
+          <t>343791</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
+          <t>6066 VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.21089</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.9536</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>-12.21334</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.93987</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>343946</t>
+          <t>343786</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>7093 REPUBLICA DE FRANCIA</t>
+          <t>6065 PERU INGLATERRA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.2293</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-76.93405</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>-12.2076</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-76.9419</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>343772</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7094 SASAKAWA</t>
+          <t>6064 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.20551</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-76.95434</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>-12.21011</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-76.93622</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>343786</t>
+          <t>343767</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6065 PERU INGLATERRA</t>
+          <t>6063 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.2076</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-76.9419</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>-12.20085</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-76.94336</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7135,42 +7135,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>343767</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6063 JOSE CARLOS MARIATEGUI</t>
+          <t>6004 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.20085</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-76.94336</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>-12.19548</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.96105</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>343772</t>
+          <t>343710</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>6064 FRANCISCO BOLOGNESI</t>
+          <t>652 24 / 7232 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.21011</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-76.93622</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>-12.21488</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.95469</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>343828</t>
+          <t>343692</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>6069 PACHACUTEC</t>
+          <t>652 22 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.21846</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-76.93606</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>-12.20616</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-76.95102</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>343927</t>
+          <t>343673</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>7091 REPUBLICA DEL PERU</t>
+          <t>652-17 CAPULLITO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-12.22856</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-76.94364</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>-12.22614</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-76.9205</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>344781</t>
+          <t>343630</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>652 10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.22662</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-76.92649</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-12.1913</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.94121</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>345709</t>
+          <t>343625</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE VILLA</t>
+          <t>652 11 PEQUEÑOS QUERUBINES</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.19737</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-76.95012</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.21539</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.94935</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>343814</t>
+          <t>343606</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>6068 MANUEL GONZALES PRADA</t>
+          <t>652 03 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.22581</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-76.93209</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>-12.23834</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-76.91759</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>343593</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>7084 PERUANO SUIZO</t>
+          <t>652 02 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.22934</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-76.92323</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>-12.23838</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-76.92429</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>344045</t>
+          <t>343588</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>7228 PERUANO CANADIENSE</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.23977</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-76.92488</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>-12.22285</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-76.9393</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>344168</t>
+          <t>343550</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.24311</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-76.94398</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-12.21923</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.92286</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>344192</t>
+          <t>343545</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BARTOLOME HERRERA</t>
+          <t>558 CASA MONTESSORI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.19965</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-76.95051</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.2322</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.92093</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>616197</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GLOBAL SCHOOL</t>
+          <t>557</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.21578</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-76.93786</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-12.2286</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.92331</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>686760</t>
+          <t>343526</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>RAINBOW KIDS</t>
+          <t>526 SANTISIMA VIRGEN DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.20461</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-76.94608</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-12.21002</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.9401</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>344026</t>
+          <t>343512</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>REPUBLICA DE BOLIVIA</t>
+          <t>517 MIS PEQUEÑITOS ANGELITOS</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.19653</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-76.94983</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>-12.21541</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-76.93717</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>343847</t>
+          <t>056638</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>MONTESSORI DE VILLA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.2239</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-76.94643</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>-12.2184</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-76.93516</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
